--- a/templates/template-tiktok.xlsx
+++ b/templates/template-tiktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\stock-hub\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A09EFD0B-6F11-4E9B-A58F-D3674BC3817A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326265DA-5656-4390-A841-B469FF3345BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
   <si>
     <t>product_id</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Identifier of the product or variant. This is used to quickly find the item in other systems.</t>
-  </si>
-  <si>
-    <t>minimum_order_quantity</t>
   </si>
   <si>
     <t>Minimum sales quantity</t>
@@ -237,7 +234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -248,7 +245,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -778,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -790,155 +786,114 @@
     <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" hidden="1">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>26</v>
-      </c>
+    <row r="4" spans="1:9">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9">
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="7"/>
+      <c r="H6" s="6"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="3"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <conditionalFormatting sqref="A4:I4">
+  <conditionalFormatting sqref="A2:I2">
     <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
@@ -949,10 +904,10 @@
       <formula>"Conditionally mandatory "</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="8">
-      <formula>IF(ISBLANK(A1),"",1)</formula>
+      <formula>IF(ISBLANK(#REF!),"",1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:I5">
+  <conditionalFormatting sqref="A3:I3">
     <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"Uneditable"</formula>
     </cfRule>
@@ -962,7 +917,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I6:I7" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I4:I5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
@@ -1002,7 +957,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A1:ZZ19911</xm:sqref>
+          <xm:sqref>A1:ZZ19909</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1017,7 +972,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -1028,7 +983,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -1039,7 +994,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
@@ -1050,7 +1005,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
         <v>3</v>
@@ -1061,7 +1016,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
         <v>3</v>
@@ -1072,7 +1027,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
         <v>3</v>
@@ -1083,7 +1038,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
         <v>3</v>
@@ -1094,7 +1049,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>3</v>
@@ -1105,7 +1060,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>3</v>
@@ -1137,7 +1092,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -1156,17 +1111,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1208,16 +1163,16 @@
         <v>14</v>
       </c>
       <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
-      </c>
-      <c r="J1" t="s">
-        <v>30</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
@@ -1236,7 +1191,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/templates/template-tiktok.xlsx
+++ b/templates/template-tiktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\stock-hub\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326265DA-5656-4390-A841-B469FF3345BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA3D287-6416-4A87-9935-326D1E466DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A3:I8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -786,104 +786,92 @@
     <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="3" t="s">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9">
       <c r="F6" s="3"/>
@@ -891,9 +879,21 @@
       <c r="H6" s="6"/>
       <c r="I6" s="3"/>
     </row>
+    <row r="7" spans="1:9">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <conditionalFormatting sqref="A2:I2">
+  <conditionalFormatting sqref="A4:I4">
     <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
@@ -907,7 +907,7 @@
       <formula>IF(ISBLANK(#REF!),"",1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:I3">
+  <conditionalFormatting sqref="A5:I5">
     <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"Uneditable"</formula>
     </cfRule>
@@ -917,7 +917,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I4:I5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I6:I7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
@@ -929,7 +929,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{00000000-000E-0000-0000-000001000000}">
-            <xm:f>AND(OR(A1="", ISBLANK(A1)),VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Mandatory")</xm:f>
+            <xm:f>AND(OR(A3="", ISBLANK(A3)),VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Mandatory")</xm:f>
             <x14:dxf>
               <border>
                 <left style="medium">
@@ -957,7 +957,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A1:ZZ19909</xm:sqref>
+          <xm:sqref>A3:ZZ19911</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/templates/template-tiktok.xlsx
+++ b/templates/template-tiktok.xlsx
@@ -8,105 +8,203 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\stock-hub\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CDE40F8-B854-4EEE-81AB-16966EA3794C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA3D287-6416-4A87-9935-326D1E466DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{83185CBE-2C69-476E-BC94-329B7DDE5D51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="HiddenStyle" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="HiddenAttr" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="SpecialProductListingType" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="SalePlatform" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="TemplateConfig" sheetId="7" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
   <si>
     <t>Product ID</t>
   </si>
   <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Uneditable</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Sales_Information</t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
+    <t>product_name</t>
+  </si>
+  <si>
     <t>Product name</t>
   </si>
   <si>
+    <t>sku_id</t>
+  </si>
+  <si>
     <t>SKU ID</t>
   </si>
   <si>
+    <t>variation_value</t>
+  </si>
+  <si>
     <t>Variation Option</t>
   </si>
   <si>
+    <t>price</t>
+  </si>
+  <si>
     <t>Retail Price (Local Currency)</t>
   </si>
   <si>
+    <t>Enter the price of the product or variant. DO NOT include any currency symbols.</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>The stock quantity of the product.</t>
+  </si>
+  <si>
+    <t>seller_sku</t>
+  </si>
+  <si>
     <t>Seller SKU</t>
   </si>
   <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Identifier of the product or variant. This is used to quickly find the item in other systems.</t>
+  </si>
+  <si>
     <t>Minimum sales quantity</t>
-  </si>
-  <si>
-    <t>Mandatory</t>
-  </si>
-  <si>
-    <t>Optional</t>
-  </si>
-  <si>
-    <t>Uneditable</t>
-  </si>
-  <si>
-    <t>Enter the price of the product or variant. DO NOT include any currency symbols.</t>
-  </si>
-  <si>
-    <t>The stock quantity of the product.</t>
-  </si>
-  <si>
-    <t>Identifier of the product or variant. This is used to quickly find the item in other systems.</t>
   </si>
   <si>
     <t>Please enter an integer within 1-20
 The minimum sales quantity will be applied to all SKUs of the product. After setting, please ensure that you have sufficient SKUs to avoid customers being unable to place an order due to the SKU number being less than the minimum sales quantity.</t>
+  </si>
+  <si>
+    <t>pfand_packaging_type</t>
+  </si>
+  <si>
+    <t>pfand_amount</t>
+  </si>
+  <si>
+    <t>sale_price</t>
+  </si>
+  <si>
+    <t>list_price</t>
+  </si>
+  <si>
+    <t>Glasses (600036)</t>
+  </si>
+  <si>
+    <t>Music Boxes (806544)</t>
+  </si>
+  <si>
+    <t>Mugs (600042)</t>
+  </si>
+  <si>
+    <t>Candles (854152)</t>
+  </si>
+  <si>
+    <t>Vase &amp; Fillers (700655)</t>
+  </si>
+  <si>
+    <t>Cards &amp; Card Stock (855560)</t>
+  </si>
+  <si>
+    <t>Oil Burners (1246096)</t>
+  </si>
+  <si>
+    <t>Party Bags &amp; Gifts (855944)</t>
+  </si>
+  <si>
+    <t>Plates (600064)</t>
+  </si>
+  <si>
+    <t>Auction product</t>
+  </si>
+  <si>
+    <t>TikTok Shop and Tokopedia (0;1)</t>
+  </si>
+  <si>
+    <t>TikTok Shop (0)</t>
+  </si>
+  <si>
+    <t>Tokopedia (1)</t>
+  </si>
+  <si>
+    <t>{"main_locale":""}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -114,20 +212,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFFF0000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFFF0000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -243,6 +398,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD3D3D3"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF0D0D0D"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -550,108 +773,429 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D72F234-9993-4CED-932E-74661ABBEFDC}">
-  <dimension ref="A3:I5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A3:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="67.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" customWidth="1"/>
-    <col min="9" max="9" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="3"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <conditionalFormatting sqref="A4:I4">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"Conditionally mandatory "</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>IF(ISBLANK(#REF!),"",1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:I5">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"Uneditable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+      <formula>"Uneditable
+Please enter the quantity of the product in the corresponding warehouse. Warehouses cannot be deleted or modified. Please copy warehouse info from [warehouse] sheet."</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I6:I7" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>1</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00000000-000E-0000-0000-000001000000}">
+            <xm:f>AND(OR(A3="", ISBLANK(A3)),VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Mandatory")</xm:f>
+            <x14:dxf>
+              <border>
+                <left style="medium">
+                  <color rgb="FFFF0000"/>
+                </left>
+                <right style="medium">
+                  <color rgb="FFFF0000"/>
+                </right>
+                <top style="medium">
+                  <color rgb="FFFF0000"/>
+                </top>
+                <bottom style="medium">
+                  <color rgb="FFFF0000"/>
+                </bottom>
+              </border>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="2" id="{00000000-000E-0000-0000-000002000000}">
+            <xm:f>VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Forbid"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFD3D3D3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A3:ZZ19911</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="5" width="35" customWidth="1"/>
+    <col min="6" max="10" width="26" customWidth="1"/>
+    <col min="11" max="12" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/templates/template-tiktok.xlsx
+++ b/templates/template-tiktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\stock-hub\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA3D287-6416-4A87-9935-326D1E466DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E386EDF-4D42-42D1-A48B-EFD8B141E72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,11 +21,16 @@
     <sheet name="TemplateConfig" sheetId="7" state="hidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="45">
   <si>
     <t>product_id</t>
   </si>
@@ -33,6 +38,42 @@
     <t>V4</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Sales_Information</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>sku_id</t>
+  </si>
+  <si>
+    <t>variation_value</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>pfand_packaging_type</t>
+  </si>
+  <si>
+    <t>pfand_amount</t>
+  </si>
+  <si>
+    <t>sale_price</t>
+  </si>
+  <si>
+    <t>list_price</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>seller_sku</t>
+  </si>
+  <si>
     <t>Product ID</t>
   </si>
   <si>
@@ -42,54 +83,30 @@
     <t>Uneditable</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>Sales_Information</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
-    <t>product_name</t>
-  </si>
-  <si>
     <t>Product name</t>
   </si>
   <si>
-    <t>sku_id</t>
-  </si>
-  <si>
     <t>SKU ID</t>
   </si>
   <si>
-    <t>variation_value</t>
-  </si>
-  <si>
     <t>Variation Option</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>Retail Price (Local Currency)</t>
   </si>
   <si>
     <t>Enter the price of the product or variant. DO NOT include any currency symbols.</t>
   </si>
   <si>
-    <t>quantity</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
     <t>The stock quantity of the product.</t>
   </si>
   <si>
-    <t>seller_sku</t>
-  </si>
-  <si>
     <t>Seller SKU</t>
   </si>
   <si>
@@ -97,6 +114,9 @@
   </si>
   <si>
     <t>Identifier of the product or variant. This is used to quickly find the item in other systems.</t>
+  </si>
+  <si>
+    <t>minimum_order_quantity</t>
   </si>
   <si>
     <t>Minimum sales quantity</t>
@@ -106,45 +126,36 @@
 The minimum sales quantity will be applied to all SKUs of the product. After setting, please ensure that you have sufficient SKUs to avoid customers being unable to place an order due to the SKU number being less than the minimum sales quantity.</t>
   </si>
   <si>
-    <t>pfand_packaging_type</t>
-  </si>
-  <si>
-    <t>pfand_amount</t>
-  </si>
-  <si>
-    <t>sale_price</t>
-  </si>
-  <si>
-    <t>list_price</t>
+    <t>{"main_locale":""}</t>
+  </si>
+  <si>
+    <t>Vase &amp; Fillers (700655)</t>
+  </si>
+  <si>
+    <t>Mugs (600042)</t>
   </si>
   <si>
     <t>Glasses (600036)</t>
   </si>
   <si>
+    <t>Candles (854152)</t>
+  </si>
+  <si>
+    <t>Cards &amp; Card Stock (855560)</t>
+  </si>
+  <si>
     <t>Music Boxes (806544)</t>
   </si>
   <si>
-    <t>Mugs (600042)</t>
-  </si>
-  <si>
-    <t>Candles (854152)</t>
-  </si>
-  <si>
-    <t>Vase &amp; Fillers (700655)</t>
-  </si>
-  <si>
-    <t>Cards &amp; Card Stock (855560)</t>
+    <t>Plates (600064)</t>
+  </si>
+  <si>
+    <t>Party Bags &amp; Gifts (855944)</t>
   </si>
   <si>
     <t>Oil Burners (1246096)</t>
   </si>
   <si>
-    <t>Party Bags &amp; Gifts (855944)</t>
-  </si>
-  <si>
-    <t>Plates (600064)</t>
-  </si>
-  <si>
     <t>Auction product</t>
   </si>
   <si>
@@ -155,9 +166,6 @@
   </si>
   <si>
     <t>Tokopedia (1)</t>
-  </si>
-  <si>
-    <t>{"main_locale":""}</t>
   </si>
 </sst>
 </file>
@@ -234,7 +242,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -245,6 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -774,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:I8"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -782,114 +791,707 @@
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:9" hidden="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="43.05" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
+      <c r="G3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" customHeight="1">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="150" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="6"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9">
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="6"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9">
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="6:9">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="6:9">
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="6:9">
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="6:9">
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="6:9">
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="6:9">
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="6:9">
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="6:9">
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="6:9">
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="6:9">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="6:9">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="6:9">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="6:9">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="6:9">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="6:9">
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="6:9">
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="6:9">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="6:9">
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="6:9">
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="6:9">
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="6:9">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="6:9">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="6:9">
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="6:9">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="6:9">
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="6:9">
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="6:9">
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="6:9">
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="6:9">
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="6:9">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="6:9">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="6:9">
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="6:9">
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="6:9">
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="6:9">
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="6:9">
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="6:9">
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="6:9">
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="6:9">
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="6:9">
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="6:9">
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="6:9">
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="6:9">
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="6:9">
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="6:9">
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="6:9">
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="6:9">
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="6:9">
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="6:9">
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="6:9">
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="6:9">
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="6:9">
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="6:9">
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" spans="6:9">
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" spans="6:9">
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="3"/>
+    </row>
+    <row r="72" spans="6:9">
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" spans="6:9">
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="3"/>
+    </row>
+    <row r="74" spans="6:9">
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" spans="6:9">
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" spans="6:9">
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" spans="6:9">
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="3"/>
+    </row>
+    <row r="78" spans="6:9">
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" spans="6:9">
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="3"/>
+    </row>
+    <row r="80" spans="6:9">
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="3"/>
+    </row>
+    <row r="81" spans="6:9">
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" spans="6:9">
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" spans="6:9">
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="3"/>
+    </row>
+    <row r="84" spans="6:9">
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="3"/>
+    </row>
+    <row r="85" spans="6:9">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="3"/>
+    </row>
+    <row r="86" spans="6:9">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="3"/>
+    </row>
+    <row r="87" spans="6:9">
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" spans="6:9">
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" spans="6:9">
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" spans="6:9">
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" spans="6:9">
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" spans="6:9">
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" spans="6:9">
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" spans="6:9">
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" spans="6:9">
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" spans="6:9">
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="3"/>
+    </row>
+    <row r="97" spans="6:9">
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="3"/>
+    </row>
+    <row r="98" spans="6:9">
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="3"/>
+    </row>
+    <row r="99" spans="6:9">
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="3"/>
+    </row>
+    <row r="100" spans="6:9">
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="3"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -904,7 +1506,7 @@
       <formula>"Conditionally mandatory "</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="8">
-      <formula>IF(ISBLANK(#REF!),"",1)</formula>
+      <formula>IF(ISBLANK(A1),"",1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:I5">
@@ -916,20 +1518,20 @@
 Please enter the quantity of the product in the corresponding warehouse. Warehouses cannot be deleted or modified. Please copy warehouse info from [warehouse] sheet."</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I6:I7" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Please enter an integer within 1-20" sqref="I6:I100" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{00000000-000E-0000-0000-000001000000}">
-            <xm:f>AND(OR(A3="", ISBLANK(A3)),VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Mandatory")</xm:f>
+            <xm:f>AND(OR(A1="", ISBLANK(A1)),VLOOKUP(INDIRECT(ADDRESS(ROW(),2)),HiddenStyle!$A$1:$ZZ$20000,COLUMN(),0)="Mandatory")</xm:f>
             <x14:dxf>
               <border>
                 <left style="medium">
@@ -957,7 +1559,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A3:ZZ19911</xm:sqref>
+          <xm:sqref>A1:ZZ19999</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -972,68 +1574,68 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1041,32 +1643,32 @@
         <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1694,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -1111,17 +1713,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1148,37 +1750,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
       <c r="L1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1186,12 +1788,12 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
